--- a/data/trans_orig/IP24-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>35284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31923</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>90452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>133205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162051</t>
+          <t>160817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43527</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58690</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>81587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35671</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>53874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>61764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>85660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92383</t>
+          <t>91758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114097</t>
+          <t>112797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85314</t>
+          <t>85358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108765</t>
+          <t>108668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181577</t>
+          <t>181739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213073</t>
+          <t>214001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64636</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>59696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>90993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118754</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>35332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>48916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69605</t>
+          <t>70823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58083</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>76090</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71016</t>
+          <t>70410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114486</t>
+          <t>114933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140807</t>
+          <t>142233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>24013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21964</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>26509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46956</t>
+          <t>47655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110286</t>
+          <t>110195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134892</t>
+          <t>134898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89080</t>
+          <t>88333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112560</t>
+          <t>111306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>206244</t>
+          <t>206757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>239515</t>
+          <t>240746</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63276</t>
+          <t>63176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45450</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>90113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121501</t>
+          <t>121138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45669</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79991</t>
+          <t>80491</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77845</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107932</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>79811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>107468</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>126229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160479</t>
+          <t>160323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>214033</t>
+          <t>213386</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261775</t>
+          <t>258566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>352060</t>
+          <t>353449</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>394220</t>
+          <t>394466</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>301371</t>
+          <t>301416</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>343686</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>663499</t>
+          <t>667455</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>723313</t>
+          <t>728528</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>150375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>314300</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42005</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34360</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90194</t>
+          <t>88934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65934</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86127</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54367</t>
+          <t>54960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75410</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125575</t>
+          <t>127551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154289</t>
+          <t>156193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59766</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60139</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67301</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90936</t>
+          <t>91701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112301</t>
+          <t>112605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134922</t>
+          <t>135041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102938</t>
+          <t>103208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127526</t>
+          <t>126511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221655</t>
+          <t>221840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252951</t>
+          <t>254482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -5509,47 +5509,47 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>36375</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54956</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>35153</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54185</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35153</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>93137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34392</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>64024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86660</t>
+          <t>87438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78315</t>
+          <t>78718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>98057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63399</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84678</t>
+          <t>84960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148044</t>
+          <t>148673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177806</t>
+          <t>176322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>53626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29871</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54790</t>
+          <t>52514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85546</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>113964</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98750</t>
+          <t>99632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123682</t>
+          <t>123944</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79630</t>
+          <t>79787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103898</t>
+          <t>103582</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187445</t>
+          <t>187149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222730</t>
+          <t>221629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57209</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>84444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61920</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81889</t>
+          <t>81145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>113189</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>115263</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>149438</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177129</t>
+          <t>176498</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>216783</t>
+          <t>216435</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>302497</t>
+          <t>300942</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>355377</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>378825</t>
+          <t>375876</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>423534</t>
+          <t>420823</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>324662</t>
+          <t>323154</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>366750</t>
+          <t>366976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>711119</t>
+          <t>715918</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>777450</t>
+          <t>776651</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>134647</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>237913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42006</t>
+          <t>42858</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,47 +8293,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>56405</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>46081</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>69034</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>16,45%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>56405</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>45206</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>69573</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64819</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84349</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>70020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>91659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141169</t>
+          <t>141167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170872</t>
+          <t>169514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>63414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27345</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>38572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86016</t>
+          <t>84422</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110786</t>
+          <t>110930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133244</t>
+          <t>132441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101555</t>
+          <t>101384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126378</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217561</t>
+          <t>220335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250573</t>
+          <t>252865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,82 +9166,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>17,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>43336</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34703</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53989</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>24,13%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>87161</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>73512</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>100392</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>43336</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34115</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>87161</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>74981</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>101418</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69447</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94246</t>
+          <t>94140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72701</t>
+          <t>72638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91540</t>
+          <t>92701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84784</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143806</t>
+          <t>143330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171774</t>
+          <t>170589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49181</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70334</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24024</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42730</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58246</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85098</t>
+          <t>82208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105181</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129925</t>
+          <t>129766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>96722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120553</t>
+          <t>119716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>207566</t>
+          <t>208930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>244633</t>
+          <t>241522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67628</t>
+          <t>69008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95013</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>81353</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97764</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129761</t>
+          <t>129155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>147861</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186263</t>
+          <t>186513</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>254627</t>
+          <t>255328</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>305149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>377563</t>
+          <t>377931</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>418649</t>
+          <t>419266</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>351445</t>
+          <t>356063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>398442</t>
+          <t>400403</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>747219</t>
+          <t>741922</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>809419</t>
+          <t>803888</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>45320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45552</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52598</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70388</t>
+          <t>69763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>43943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72251</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102014</t>
+          <t>100323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136287</t>
+          <t>135412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23163</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>57988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>73915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52898</t>
+          <t>50838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82276</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>87450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123291</t>
+          <t>121221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80789</t>
+          <t>81681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107510</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137998</t>
+          <t>140251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199194</t>
+          <t>199611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239709</t>
+          <t>239061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>55665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32880</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53565</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65177</t>
+          <t>68299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92420</t>
+          <t>93245</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>44590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>93374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>57928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>85454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166936</t>
+          <t>170624</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40797</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110048</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53479</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81804</t>
+          <t>81443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44910</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>69146</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52104</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61404</t>
+          <t>60956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87348</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69398</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90740</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85364</t>
+          <t>84547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137707</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>168863</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>68836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>131762</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>105673</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,47 +14628,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>184903</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>164197</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>184903</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>160068</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>208894</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>277124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>340459</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>267540</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>338461</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>589720</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>677064</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125608</t>
+          <t>124635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>368345</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
